--- a/Iago/todos_pontos_gps.xlsx
+++ b/Iago/todos_pontos_gps.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H445"/>
+  <dimension ref="A1:J445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,16 @@
           <t>longitude</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Px</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Py</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -498,6 +508,12 @@
       </c>
       <c r="H2" t="n">
         <v>-41.76452632739855</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -529,6 +545,12 @@
       <c r="H3" t="n">
         <v>-41.76414848213214</v>
       </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -559,6 +581,12 @@
       <c r="H4" t="n">
         <v>-41.76407832326416</v>
       </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -589,6 +617,12 @@
       <c r="H5" t="n">
         <v>-41.76401252017587</v>
       </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -619,6 +653,12 @@
       <c r="H6" t="n">
         <v>-41.7641432414072</v>
       </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -649,6 +689,12 @@
       <c r="H7" t="n">
         <v>-41.7640747164242</v>
       </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -679,6 +725,12 @@
       <c r="H8" t="n">
         <v>-41.76400752778195</v>
       </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -709,6 +761,12 @@
       <c r="H9" t="n">
         <v>-41.76388883667183</v>
       </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -739,6 +797,12 @@
       <c r="H10" t="n">
         <v>-41.76382062876046</v>
       </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -769,6 +833,12 @@
       <c r="H11" t="n">
         <v>-41.76375274063191</v>
       </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -799,6 +869,12 @@
       <c r="H12" t="n">
         <v>-41.76389143989205</v>
       </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -829,6 +905,12 @@
       <c r="H13" t="n">
         <v>-41.76382242363506</v>
       </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -859,6 +941,12 @@
       <c r="H14" t="n">
         <v>-41.76375598959515</v>
       </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -889,6 +977,12 @@
       <c r="H15" t="n">
         <v>-41.76414407470261</v>
       </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -919,6 +1013,12 @@
       <c r="H16" t="n">
         <v>-41.76407706002249</v>
       </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -949,6 +1049,12 @@
       <c r="H17" t="n">
         <v>-41.76401022572213</v>
       </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -979,6 +1085,12 @@
       <c r="H18" t="n">
         <v>-41.76389088886899</v>
       </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1009,6 +1121,12 @@
       <c r="H19" t="n">
         <v>-41.76382187261198</v>
       </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1039,6 +1157,12 @@
       <c r="H20" t="n">
         <v>-41.76414502169629</v>
       </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1069,6 +1193,12 @@
       <c r="H21" t="n">
         <v>-41.76407800701617</v>
       </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1099,6 +1229,12 @@
       <c r="H22" t="n">
         <v>-41.76401117285308</v>
       </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1129,6 +1265,12 @@
       <c r="H23" t="n">
         <v>-41.76414462572568</v>
       </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1159,6 +1301,12 @@
       <c r="H24" t="n">
         <v>-41.7640776111142</v>
       </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1189,6 +1337,12 @@
       <c r="H25" t="n">
         <v>-41.76401077681383</v>
       </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1219,6 +1373,12 @@
       <c r="H26" t="n">
         <v>-41.76375543843481</v>
       </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1249,6 +1409,12 @@
       <c r="H27" t="n">
         <v>-41.76389368942245</v>
       </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1279,6 +1445,12 @@
       <c r="H28" t="n">
         <v>-41.76382523462144</v>
       </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1309,6 +1481,12 @@
       <c r="H29" t="n">
         <v>-41.76375754156109</v>
       </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1339,6 +1517,12 @@
       <c r="H30" t="n">
         <v>-41.76414439994213</v>
       </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1369,6 +1553,12 @@
       <c r="H31" t="n">
         <v>-41.76407594524407</v>
       </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1399,6 +1589,12 @@
       <c r="H32" t="n">
         <v>-41.76400749034011</v>
       </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1429,6 +1625,12 @@
       <c r="H33" t="n">
         <v>-41.76389267852711</v>
       </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1459,6 +1661,12 @@
       <c r="H34" t="n">
         <v>-41.76382422358883</v>
       </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1489,6 +1697,12 @@
       <c r="H35" t="n">
         <v>-41.7641467816</v>
       </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1519,6 +1733,12 @@
       <c r="H36" t="n">
         <v>-41.76407832690195</v>
       </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1549,6 +1769,12 @@
       <c r="H37" t="n">
         <v>-41.76400987206663</v>
       </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1579,6 +1805,12 @@
       <c r="H38" t="n">
         <v>-41.7641454109061</v>
       </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1609,6 +1841,12 @@
       <c r="H39" t="n">
         <v>-41.76407695607077</v>
       </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1639,6 +1877,12 @@
       <c r="H40" t="n">
         <v>-41.76400850130408</v>
       </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1669,6 +1913,12 @@
       <c r="H41" t="n">
         <v>-41.76375653066576</v>
       </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1699,6 +1949,12 @@
       <c r="H42" t="n">
         <v>-41.76389282060705</v>
       </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1729,6 +1985,12 @@
       <c r="H43" t="n">
         <v>-41.76382465621195</v>
       </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1759,6 +2021,12 @@
       <c r="H44" t="n">
         <v>-41.763755589369</v>
       </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1789,6 +2057,12 @@
       <c r="H45" t="n">
         <v>-41.76414336886732</v>
       </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1819,6 +2093,12 @@
       <c r="H46" t="n">
         <v>-41.76407571994098</v>
       </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1849,6 +2129,12 @@
       <c r="H47" t="n">
         <v>-41.76400727677406</v>
       </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1879,6 +2165,12 @@
       <c r="H48" t="n">
         <v>-41.7638917119717</v>
       </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1909,6 +2201,12 @@
       <c r="H49" t="n">
         <v>-41.76414632344368</v>
       </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1939,6 +2237,12 @@
       <c r="H50" t="n">
         <v>-41.76407867451734</v>
       </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1969,6 +2273,12 @@
       <c r="H51" t="n">
         <v>-41.76401023128178</v>
       </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1999,6 +2309,12 @@
       <c r="H52" t="n">
         <v>-41.76414519819802</v>
       </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2029,6 +2345,12 @@
       <c r="H53" t="n">
         <v>-41.76407754934031</v>
       </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2059,6 +2381,12 @@
       <c r="H54" t="n">
         <v>-41.76382354743932</v>
       </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2089,6 +2417,12 @@
       <c r="H55" t="n">
         <v>-41.76400910603611</v>
       </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2119,6 +2453,12 @@
       <c r="H56" t="n">
         <v>-41.76414503058487</v>
       </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2149,6 +2489,12 @@
       <c r="H57" t="n">
         <v>-41.76407738172717</v>
       </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2179,6 +2525,12 @@
       <c r="H58" t="n">
         <v>-41.76400893842297</v>
       </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2209,6 +2561,12 @@
       <c r="H59" t="n">
         <v>-41.76389337368925</v>
       </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2239,6 +2597,12 @@
       <c r="H60" t="n">
         <v>-41.7638252090196</v>
       </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2269,6 +2633,12 @@
       <c r="H61" t="n">
         <v>-41.7637561424512</v>
       </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2299,6 +2669,12 @@
       <c r="H62" t="n">
         <v>-41.76414447763995</v>
       </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2329,6 +2705,12 @@
       <c r="H63" t="n">
         <v>-41.76407682878225</v>
       </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2359,6 +2741,12 @@
       <c r="H64" t="n">
         <v>-41.76400838547805</v>
       </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2389,6 +2777,12 @@
       <c r="H65" t="n">
         <v>-41.76375448059638</v>
       </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2419,6 +2813,12 @@
       <c r="H66" t="n">
         <v>-41.76410481911366</v>
       </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2449,6 +2849,12 @@
       <c r="H67" t="n">
         <v>-41.76401588125871</v>
       </c>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2479,6 +2885,12 @@
       <c r="H68" t="n">
         <v>-41.76417669872757</v>
       </c>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2509,6 +2921,12 @@
       <c r="H69" t="n">
         <v>-41.76408335831638</v>
       </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2539,6 +2957,12 @@
       <c r="H70" t="n">
         <v>-41.76399298226239</v>
       </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2569,6 +2993,12 @@
       <c r="H71" t="n">
         <v>-41.76390221071827</v>
       </c>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2599,6 +3029,12 @@
       <c r="H72" t="n">
         <v>-41.76381457210544</v>
       </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2629,6 +3065,12 @@
       <c r="H73" t="n">
         <v>-41.76372263190233</v>
       </c>
+      <c r="I73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2659,6 +3101,12 @@
       <c r="H74" t="n">
         <v>-41.76428711308066</v>
       </c>
+      <c r="I74" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2689,6 +3137,12 @@
       <c r="H75" t="n">
         <v>-41.76419429882854</v>
       </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2719,6 +3173,12 @@
       <c r="H76" t="n">
         <v>-41.76362868782299</v>
       </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2749,6 +3209,12 @@
       <c r="H77" t="n">
         <v>-41.76381566186544</v>
       </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2779,6 +3245,12 @@
       <c r="H78" t="n">
         <v>-41.76372334868533</v>
       </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2809,6 +3281,12 @@
       <c r="H79" t="n">
         <v>-41.76363097222131</v>
       </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2839,6 +3317,12 @@
       <c r="H80" t="n">
         <v>-41.76414367605513</v>
       </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2869,6 +3353,12 @@
       <c r="H81" t="n">
         <v>-41.76407479618115</v>
       </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2899,6 +3389,12 @@
       <c r="H82" t="n">
         <v>-41.7640068190982</v>
       </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2929,6 +3425,12 @@
       <c r="H83" t="n">
         <v>-41.76388902460172</v>
       </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2959,6 +3461,12 @@
       <c r="H84" t="n">
         <v>-41.76414767608588</v>
       </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2989,6 +3497,12 @@
       <c r="H85" t="n">
         <v>-41.76382170685206</v>
       </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3019,6 +3533,12 @@
       <c r="H86" t="n">
         <v>-41.76407993659216</v>
       </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3049,6 +3569,12 @@
       <c r="H87" t="n">
         <v>-41.76401153210255</v>
       </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3079,6 +3605,12 @@
       <c r="H88" t="n">
         <v>-41.76428556996898</v>
       </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3109,6 +3641,12 @@
       <c r="H89" t="n">
         <v>-41.76420019188572</v>
       </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3139,6 +3677,12 @@
       <c r="H90" t="n">
         <v>-41.76410566829868</v>
       </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3169,6 +3713,12 @@
       <c r="H91" t="n">
         <v>-41.76401385692846</v>
       </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3199,6 +3749,12 @@
       <c r="H92" t="n">
         <v>-41.76417857380526</v>
       </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3229,6 +3785,12 @@
       <c r="H93" t="n">
         <v>-41.76408625221705</v>
       </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3259,6 +3821,12 @@
       <c r="H94" t="n">
         <v>-41.76398574452498</v>
       </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3289,6 +3857,12 @@
       <c r="H95" t="n">
         <v>-41.7639047166103</v>
       </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3319,6 +3893,12 @@
       <c r="H96" t="n">
         <v>-41.76375237822511</v>
       </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3349,6 +3929,12 @@
       <c r="H97" t="n">
         <v>-41.76389190731446</v>
       </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3379,6 +3965,12 @@
       <c r="H98" t="n">
         <v>-41.76382374237026</v>
       </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3409,6 +4001,12 @@
       <c r="H99" t="n">
         <v>-41.7637546758705</v>
       </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3439,6 +4037,12 @@
       <c r="H100" t="n">
         <v>-41.76414327092139</v>
       </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3469,6 +4073,12 @@
       <c r="H101" t="n">
         <v>-41.76407562199505</v>
       </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3499,6 +4109,12 @@
       <c r="H102" t="n">
         <v>-41.76400717875949</v>
       </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3529,6 +4145,12 @@
       <c r="H103" t="n">
         <v>-41.76389161395714</v>
       </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3559,6 +4181,12 @@
       <c r="H104" t="n">
         <v>-41.76382344956203</v>
       </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3589,6 +4217,12 @@
       <c r="H105" t="n">
         <v>-41.76414644383411</v>
       </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3619,6 +4253,12 @@
       <c r="H106" t="n">
         <v>-41.76407879542256</v>
       </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3649,6 +4289,12 @@
       <c r="H107" t="n">
         <v>-41.76401035222132</v>
       </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3679,6 +4325,12 @@
       <c r="H108" t="n">
         <v>-41.76414614663309</v>
       </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3709,6 +4361,12 @@
       <c r="H109" t="n">
         <v>-41.76407849815289</v>
       </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3739,6 +4397,12 @@
       <c r="H110" t="n">
         <v>-41.76401005502029</v>
       </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3769,6 +4433,12 @@
       <c r="H111" t="n">
         <v>-41.76414356393553</v>
       </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3799,6 +4469,12 @@
       <c r="H112" t="n">
         <v>-41.76407591545534</v>
       </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3829,6 +4505,12 @@
       <c r="H113" t="n">
         <v>-41.76400747225409</v>
       </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3859,6 +4541,12 @@
       <c r="H114" t="n">
         <v>-41.76375438285636</v>
       </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3889,6 +4577,12 @@
       <c r="H115" t="n">
         <v>-41.76414572241808</v>
       </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3919,6 +4613,12 @@
       <c r="H116" t="n">
         <v>-41.7640757001047</v>
       </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3949,6 +4649,12 @@
       <c r="H117" t="n">
         <v>-41.76401060319489</v>
       </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3979,6 +4685,12 @@
       <c r="H118" t="n">
         <v>-41.76414518779941</v>
       </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4009,6 +4721,12 @@
       <c r="H119" t="n">
         <v>-41.7640751654174</v>
       </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4039,6 +4757,12 @@
       <c r="H120" t="n">
         <v>-41.76401006850759</v>
       </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4069,6 +4793,12 @@
       <c r="H121" t="n">
         <v>-41.76389089991964</v>
       </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4099,6 +4829,12 @@
       <c r="H122" t="n">
         <v>-41.76382250895166</v>
       </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4129,6 +4865,12 @@
       <c r="H123" t="n">
         <v>-41.76401089819952</v>
       </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4159,6 +4901,12 @@
       <c r="H124" t="n">
         <v>-41.76375694132483</v>
       </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4189,6 +4937,12 @@
       <c r="H125" t="n">
         <v>-41.76411807627017</v>
       </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4219,6 +4973,12 @@
       <c r="H126" t="n">
         <v>-41.76407664956934</v>
       </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4249,6 +5009,12 @@
       <c r="H127" t="n">
         <v>-41.76403098480238</v>
       </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4279,6 +5045,12 @@
       <c r="H128" t="n">
         <v>-41.76399368778882</v>
       </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4309,6 +5081,12 @@
       <c r="H129" t="n">
         <v>-41.76395092587975</v>
       </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4339,6 +5117,12 @@
       <c r="H130" t="n">
         <v>-41.76430444739948</v>
       </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4369,6 +5153,12 @@
       <c r="H131" t="n">
         <v>-41.76420732580869</v>
       </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4399,6 +5189,12 @@
       <c r="H132" t="n">
         <v>-41.76416078941219</v>
       </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4429,6 +5225,12 @@
       <c r="H133" t="n">
         <v>-41.76411851541387</v>
       </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4459,6 +5261,12 @@
       <c r="H134" t="n">
         <v>-41.76407863309452</v>
       </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4489,6 +5297,12 @@
       <c r="H135" t="n">
         <v>-41.76403731968013</v>
       </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4519,6 +5333,12 @@
       <c r="H136" t="n">
         <v>-41.76399668663646</v>
       </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4549,6 +5369,12 @@
       <c r="H137" t="n">
         <v>-41.76395121738386</v>
       </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4579,6 +5405,12 @@
       <c r="H138" t="n">
         <v>-41.76386583996982</v>
       </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4609,6 +5441,12 @@
       <c r="H139" t="n">
         <v>-41.76390911353826</v>
       </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4639,6 +5477,12 @@
       <c r="H140" t="n">
         <v>-41.76386707963444</v>
       </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4669,6 +5513,12 @@
       <c r="H141" t="n">
         <v>-41.7638257659455</v>
       </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4699,6 +5549,12 @@
       <c r="H142" t="n">
         <v>-41.76374021055404</v>
       </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4729,6 +5585,12 @@
       <c r="H143" t="n">
         <v>-41.76430443216193</v>
       </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4759,6 +5621,12 @@
       <c r="H144" t="n">
         <v>-41.76420526413955</v>
       </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4789,6 +5657,12 @@
       <c r="H145" t="n">
         <v>-41.76416107202773</v>
       </c>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4819,6 +5693,12 @@
       <c r="H146" t="n">
         <v>-41.76411983222722</v>
       </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4849,6 +5729,12 @@
       <c r="H147" t="n">
         <v>-41.76407840552638</v>
       </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -4879,6 +5765,12 @@
       <c r="H148" t="n">
         <v>-41.76403274069079</v>
       </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4909,6 +5801,12 @@
       <c r="H149" t="n">
         <v>-41.76382027603157</v>
       </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4939,6 +5837,12 @@
       <c r="H150" t="n">
         <v>-41.76399544367722</v>
       </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -4969,6 +5873,12 @@
       <c r="H151" t="n">
         <v>-41.76395268176815</v>
       </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -4999,6 +5909,12 @@
       <c r="H152" t="n">
         <v>-41.76386759572095</v>
       </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5029,6 +5945,12 @@
       <c r="H153" t="n">
         <v>-41.76382203205725</v>
       </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5059,6 +5981,12 @@
       <c r="H154" t="n">
         <v>-41.76378042844287</v>
       </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5089,6 +6017,12 @@
       <c r="H155" t="n">
         <v>-41.76374007931885</v>
       </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5119,6 +6053,12 @@
       <c r="H156" t="n">
         <v>-41.76430269147676</v>
       </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5149,6 +6089,12 @@
       <c r="H157" t="n">
         <v>-41.76420556992029</v>
       </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5179,6 +6125,12 @@
       <c r="H158" t="n">
         <v>-41.76415903352379</v>
       </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5209,6 +6161,12 @@
       <c r="H159" t="n">
         <v>-41.76411675945683</v>
       </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5239,6 +6197,12 @@
       <c r="H160" t="n">
         <v>-41.76377867241719</v>
       </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5269,6 +6233,12 @@
       <c r="H161" t="n">
         <v>-41.76407687720611</v>
       </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5299,6 +6269,12 @@
       <c r="H162" t="n">
         <v>-41.76403556379172</v>
       </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5329,6 +6305,12 @@
       <c r="H163" t="n">
         <v>-41.76399493074805</v>
       </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5359,6 +6341,12 @@
       <c r="H164" t="n">
         <v>-41.76394946149544</v>
       </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5389,6 +6377,12 @@
       <c r="H165" t="n">
         <v>-41.76390735764986</v>
       </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5419,6 +6413,12 @@
       <c r="H166" t="n">
         <v>-41.76386532374604</v>
       </c>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5449,6 +6449,12 @@
       <c r="H167" t="n">
         <v>-41.7638240100571</v>
       </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5479,6 +6485,12 @@
       <c r="H168" t="n">
         <v>-41.76373845466563</v>
       </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5509,6 +6521,12 @@
       <c r="H169" t="n">
         <v>-41.7643026762392</v>
       </c>
+      <c r="I169" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5539,6 +6557,12 @@
       <c r="H170" t="n">
         <v>-41.76420350825114</v>
       </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5569,6 +6593,12 @@
       <c r="H171" t="n">
         <v>-41.76373832356771</v>
       </c>
+      <c r="I171" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5599,6 +6629,12 @@
       <c r="H172" t="n">
         <v>-41.76420451595482</v>
       </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5629,6 +6665,12 @@
       <c r="H173" t="n">
         <v>-41.76411771952598</v>
       </c>
+      <c r="I173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -5659,6 +6701,12 @@
       <c r="H174" t="n">
         <v>-41.76403632275255</v>
       </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -5689,6 +6737,12 @@
       <c r="H175" t="n">
         <v>-41.76399519754261</v>
       </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5719,6 +6773,12 @@
       <c r="H176" t="n">
         <v>-41.76395066745899</v>
       </c>
+      <c r="I176" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5749,6 +6809,12 @@
       <c r="H177" t="n">
         <v>-41.76386544832338</v>
       </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5779,6 +6845,12 @@
       <c r="H178" t="n">
         <v>-41.76378372339334</v>
       </c>
+      <c r="I178" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5809,6 +6881,12 @@
       <c r="H179" t="n">
         <v>-41.7643059271243</v>
       </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -5839,6 +6917,12 @@
       <c r="H180" t="n">
         <v>-41.76420642830276</v>
       </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -5869,6 +6953,12 @@
       <c r="H181" t="n">
         <v>-41.76415984488947</v>
       </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -5899,6 +6989,12 @@
       <c r="H182" t="n">
         <v>-41.76373835713153</v>
       </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -5929,6 +7025,12 @@
       <c r="H183" t="n">
         <v>-41.76411958674466</v>
       </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -5959,6 +7061,12 @@
       <c r="H184" t="n">
         <v>-41.76407764821285</v>
       </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -5989,6 +7097,12 @@
       <c r="H185" t="n">
         <v>-41.76403807795458</v>
       </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6019,6 +7133,12 @@
       <c r="H186" t="n">
         <v>-41.76399695281327</v>
       </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6049,6 +7169,12 @@
       <c r="H187" t="n">
         <v>-41.76395242272965</v>
       </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6079,6 +7205,12 @@
       <c r="H188" t="n">
         <v>-41.76386720366268</v>
       </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6109,6 +7241,12 @@
       <c r="H189" t="n">
         <v>-41.76378547873264</v>
       </c>
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6139,6 +7277,12 @@
       <c r="H190" t="n">
         <v>-41.76374011233356</v>
       </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6169,6 +7313,12 @@
       <c r="H191" t="n">
         <v>-41.76369849032429</v>
       </c>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -6199,6 +7349,12 @@
       <c r="H192" t="n">
         <v>-41.76430397287308</v>
       </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -6229,6 +7385,12 @@
       <c r="H193" t="n">
         <v>-41.76369564460725</v>
       </c>
+      <c r="I193" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -6259,6 +7421,12 @@
       <c r="H194" t="n">
         <v>-41.76469742784722</v>
       </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -6289,6 +7457,12 @@
       <c r="H195" t="n">
         <v>-41.76462841153874</v>
       </c>
+      <c r="I195" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -6319,6 +7493,12 @@
       <c r="H196" t="n">
         <v>-41.7645619776018</v>
       </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -6349,6 +7529,12 @@
       <c r="H197" t="n">
         <v>-41.76495006234892</v>
       </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -6379,6 +7565,12 @@
       <c r="H198" t="n">
         <v>-41.76488304770312</v>
       </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -6409,6 +7601,12 @@
       <c r="H199" t="n">
         <v>-41.76481621343707</v>
       </c>
+      <c r="I199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -6439,6 +7637,12 @@
       <c r="H200" t="n">
         <v>-41.76469687634369</v>
       </c>
+      <c r="I200" t="n">
+        <v>1</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -6469,6 +7673,12 @@
       <c r="H201" t="n">
         <v>-41.76462786006954</v>
       </c>
+      <c r="I201" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -6499,6 +7709,12 @@
       <c r="H202" t="n">
         <v>-41.76495061378381</v>
       </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -6529,6 +7745,12 @@
       <c r="H203" t="n">
         <v>-41.76488359913801</v>
       </c>
+      <c r="I203" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -6559,6 +7781,12 @@
       <c r="H204" t="n">
         <v>-41.76481676487196</v>
       </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -6589,6 +7817,12 @@
       <c r="H205" t="n">
         <v>-41.76456142611543</v>
       </c>
+      <c r="I205" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -6619,6 +7853,12 @@
       <c r="H206" t="n">
         <v>-41.76469987169081</v>
       </c>
+      <c r="I206" t="n">
+        <v>1</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -6649,6 +7889,12 @@
       <c r="H207" t="n">
         <v>-41.76463141682117</v>
       </c>
+      <c r="I207" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -6679,6 +7925,12 @@
       <c r="H208" t="n">
         <v>-41.76456372373508</v>
       </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -6709,6 +7961,12 @@
       <c r="H209" t="n">
         <v>-41.76495058221049</v>
       </c>
+      <c r="I209" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -6739,6 +7997,12 @@
       <c r="H210" t="n">
         <v>-41.76488212737517</v>
       </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -6769,6 +8033,12 @@
       <c r="H211" t="n">
         <v>-41.76481367267711</v>
       </c>
+      <c r="I211" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -6799,6 +8069,12 @@
       <c r="H212" t="n">
         <v>-41.76469886076116</v>
       </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -6829,6 +8105,12 @@
       <c r="H213" t="n">
         <v>-41.76463040590868</v>
       </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -6859,6 +8141,12 @@
       <c r="H214" t="n">
         <v>-41.76495159317446</v>
       </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -6889,6 +8177,12 @@
       <c r="H215" t="n">
         <v>-41.76488313833914</v>
       </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -6919,6 +8213,12 @@
       <c r="H216" t="n">
         <v>-41.76481468357245</v>
       </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -6949,6 +8249,12 @@
       <c r="H217" t="n">
         <v>-41.76456271280543</v>
       </c>
+      <c r="I217" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -6979,6 +8285,12 @@
       <c r="H218" t="n">
         <v>-41.76469959655679</v>
       </c>
+      <c r="I218" t="n">
+        <v>1</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -7009,6 +8321,12 @@
       <c r="H219" t="n">
         <v>-41.76463081855824</v>
       </c>
+      <c r="I219" t="n">
+        <v>1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7039,6 +8357,12 @@
       <c r="H220" t="n">
         <v>-41.76456420596606</v>
       </c>
+      <c r="I220" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7069,6 +8393,12 @@
       <c r="H221" t="n">
         <v>-41.76495141427042</v>
       </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7099,6 +8429,12 @@
       <c r="H222" t="n">
         <v>-41.76488329503889</v>
       </c>
+      <c r="I222" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -7129,6 +8465,12 @@
       <c r="H223" t="n">
         <v>-41.76481668552684</v>
       </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -7159,6 +8501,12 @@
       <c r="H224" t="n">
         <v>-41.76469904144977</v>
       </c>
+      <c r="I224" t="n">
+        <v>1</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -7189,6 +8537,12 @@
       <c r="H225" t="n">
         <v>-41.76463026348555</v>
       </c>
+      <c r="I225" t="n">
+        <v>1</v>
+      </c>
+      <c r="J225" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -7219,6 +8573,12 @@
       <c r="H226" t="n">
         <v>-41.76495196927448</v>
       </c>
+      <c r="I226" t="n">
+        <v>1</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -7249,6 +8609,12 @@
       <c r="H227" t="n">
         <v>-41.76488385004295</v>
       </c>
+      <c r="I227" t="n">
+        <v>1</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -7279,6 +8645,12 @@
       <c r="H228" t="n">
         <v>-41.76481724066817</v>
       </c>
+      <c r="I228" t="n">
+        <v>1</v>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7309,6 +8681,12 @@
       <c r="H229" t="n">
         <v>-41.76456365086764</v>
       </c>
+      <c r="I229" t="n">
+        <v>1</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -7339,6 +8717,12 @@
       <c r="H230" t="n">
         <v>-41.76501070083142</v>
       </c>
+      <c r="I230" t="n">
+        <v>3</v>
+      </c>
+      <c r="J230" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -7369,6 +8753,12 @@
       <c r="H231" t="n">
         <v>-41.7649175516104</v>
       </c>
+      <c r="I231" t="n">
+        <v>3</v>
+      </c>
+      <c r="J231" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -7399,6 +8789,12 @@
       <c r="H232" t="n">
         <v>-41.76482694006064</v>
       </c>
+      <c r="I232" t="n">
+        <v>3</v>
+      </c>
+      <c r="J232" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -7429,6 +8825,12 @@
       <c r="H233" t="n">
         <v>-41.76473687496954</v>
       </c>
+      <c r="I233" t="n">
+        <v>3</v>
+      </c>
+      <c r="J233" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -7459,6 +8861,12 @@
       <c r="H234" t="n">
         <v>-41.76464873550777</v>
       </c>
+      <c r="I234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J234" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -7489,6 +8897,12 @@
       <c r="H235" t="n">
         <v>-41.76455670538076</v>
       </c>
+      <c r="I235" t="n">
+        <v>3</v>
+      </c>
+      <c r="J235" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -7519,6 +8933,12 @@
       <c r="H236" t="n">
         <v>-41.76446507720442</v>
       </c>
+      <c r="I236" t="n">
+        <v>3</v>
+      </c>
+      <c r="J236" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -7549,6 +8969,12 @@
       <c r="H237" t="n">
         <v>-41.76495005236214</v>
       </c>
+      <c r="I237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J237" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -7579,6 +9005,12 @@
       <c r="H238" t="n">
         <v>-41.76488240395058</v>
       </c>
+      <c r="I238" t="n">
+        <v>1</v>
+      </c>
+      <c r="J238" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -7609,6 +9041,12 @@
       <c r="H239" t="n">
         <v>-41.76481396074934</v>
       </c>
+      <c r="I239" t="n">
+        <v>1</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -7639,6 +9077,12 @@
       <c r="H240" t="n">
         <v>-41.76469839574107</v>
       </c>
+      <c r="I240" t="n">
+        <v>1</v>
+      </c>
+      <c r="J240" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -7669,6 +9113,12 @@
       <c r="H241" t="n">
         <v>-41.76463023091698</v>
       </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+      <c r="J241" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -7699,6 +9149,12 @@
       <c r="H242" t="n">
         <v>-41.76469782474445</v>
       </c>
+      <c r="I242" t="n">
+        <v>1</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -7729,6 +9185,12 @@
       <c r="H243" t="n">
         <v>-41.7646294337593</v>
       </c>
+      <c r="I243" t="n">
+        <v>1</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -7759,6 +9221,12 @@
       <c r="H244" t="n">
         <v>-41.76456386621827</v>
       </c>
+      <c r="I244" t="n">
+        <v>1</v>
+      </c>
+      <c r="J244" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -7789,6 +9257,12 @@
       <c r="H245" t="n">
         <v>-41.76495157855464</v>
       </c>
+      <c r="I245" t="n">
+        <v>1</v>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -7819,6 +9293,12 @@
       <c r="H246" t="n">
         <v>-41.76488155624126</v>
       </c>
+      <c r="I246" t="n">
+        <v>1</v>
+      </c>
+      <c r="J246" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -7849,6 +9329,12 @@
       <c r="H247" t="n">
         <v>-41.76481645933146</v>
       </c>
+      <c r="I247" t="n">
+        <v>1</v>
+      </c>
+      <c r="J247" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -7879,6 +9365,12 @@
       <c r="H248" t="n">
         <v>-41.76469729070919</v>
       </c>
+      <c r="I248" t="n">
+        <v>1</v>
+      </c>
+      <c r="J248" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -7909,6 +9401,12 @@
       <c r="H249" t="n">
         <v>-41.7646288997412</v>
       </c>
+      <c r="I249" t="n">
+        <v>1</v>
+      </c>
+      <c r="J249" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -7939,6 +9437,12 @@
       <c r="H250" t="n">
         <v>-41.76495211255557</v>
       </c>
+      <c r="I250" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -7969,6 +9473,12 @@
       <c r="H251" t="n">
         <v>-41.7648820902422</v>
       </c>
+      <c r="I251" t="n">
+        <v>1</v>
+      </c>
+      <c r="J251" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -7999,6 +9509,12 @@
       <c r="H252" t="n">
         <v>-41.76481699326375</v>
       </c>
+      <c r="I252" t="n">
+        <v>1</v>
+      </c>
+      <c r="J252" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8029,6 +9545,12 @@
       <c r="H253" t="n">
         <v>-41.76456333218302</v>
       </c>
+      <c r="I253" t="n">
+        <v>1</v>
+      </c>
+      <c r="J253" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -8059,6 +9581,12 @@
       <c r="H254" t="n">
         <v>-41.76480013287075</v>
       </c>
+      <c r="I254" t="n">
+        <v>1</v>
+      </c>
+      <c r="J254" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -8089,6 +9617,12 @@
       <c r="H255" t="n">
         <v>-41.76475720037995</v>
       </c>
+      <c r="I255" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -8119,6 +9653,12 @@
       <c r="H256" t="n">
         <v>-41.76467215354201</v>
       </c>
+      <c r="I256" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -8149,6 +9689,12 @@
       <c r="H257" t="n">
         <v>-41.7651051275021</v>
       </c>
+      <c r="I257" t="n">
+        <v>1</v>
+      </c>
+      <c r="J257" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -8179,6 +9725,12 @@
       <c r="H258" t="n">
         <v>-41.76462661149917</v>
       </c>
+      <c r="I258" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8209,6 +9761,12 @@
       <c r="H259" t="n">
         <v>-41.76501364665648</v>
       </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -8239,6 +9797,12 @@
       <c r="H260" t="n">
         <v>-41.76496731435404</v>
       </c>
+      <c r="I260" t="n">
+        <v>1</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -8269,6 +9833,12 @@
       <c r="H261" t="n">
         <v>-41.76492468385175</v>
       </c>
+      <c r="I261" t="n">
+        <v>1</v>
+      </c>
+      <c r="J261" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -8299,6 +9869,12 @@
       <c r="H262" t="n">
         <v>-41.76488500528326</v>
       </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -8329,6 +9905,12 @@
       <c r="H263" t="n">
         <v>-41.76484347274317</v>
       </c>
+      <c r="I263" t="n">
+        <v>1</v>
+      </c>
+      <c r="J263" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -8359,6 +9941,12 @@
       <c r="H264" t="n">
         <v>-41.76480279968375</v>
       </c>
+      <c r="I264" t="n">
+        <v>1</v>
+      </c>
+      <c r="J264" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -8389,6 +9977,12 @@
       <c r="H265" t="n">
         <v>-41.76475771315469</v>
       </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -8419,6 +10013,12 @@
       <c r="H266" t="n">
         <v>-41.76471539867731</v>
       </c>
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -8449,6 +10049,12 @@
       <c r="H267" t="n">
         <v>-41.764673565041</v>
       </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -8479,6 +10085,12 @@
       <c r="H268" t="n">
         <v>-41.76459019534691</v>
       </c>
+      <c r="I268" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -8509,6 +10121,12 @@
       <c r="H269" t="n">
         <v>-41.76458489379186</v>
       </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -8539,6 +10157,12 @@
       <c r="H270" t="n">
         <v>-41.76450514707187</v>
       </c>
+      <c r="I270" t="n">
+        <v>1</v>
+      </c>
+      <c r="J270" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -8569,6 +10193,12 @@
       <c r="H271" t="n">
         <v>-41.76440378687014</v>
       </c>
+      <c r="I271" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -8599,6 +10229,12 @@
       <c r="H272" t="n">
         <v>-41.76510483819439</v>
       </c>
+      <c r="I272" t="n">
+        <v>1</v>
+      </c>
+      <c r="J272" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -8629,6 +10265,12 @@
       <c r="H273" t="n">
         <v>-41.76501153646051</v>
       </c>
+      <c r="I273" t="n">
+        <v>1</v>
+      </c>
+      <c r="J273" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -8659,6 +10301,12 @@
       <c r="H274" t="n">
         <v>-41.76496727560808</v>
       </c>
+      <c r="I274" t="n">
+        <v>1</v>
+      </c>
+      <c r="J274" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -8689,6 +10337,12 @@
       <c r="H275" t="n">
         <v>-41.76492605959052</v>
       </c>
+      <c r="I275" t="n">
+        <v>1</v>
+      </c>
+      <c r="J275" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -8719,6 +10373,12 @@
       <c r="H276" t="n">
         <v>-41.76488474624477</v>
       </c>
+      <c r="I276" t="n">
+        <v>1</v>
+      </c>
+      <c r="J276" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -8749,6 +10409,12 @@
       <c r="H277" t="n">
         <v>-41.76483911771849</v>
       </c>
+      <c r="I277" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -8779,6 +10445,12 @@
       <c r="H278" t="n">
         <v>-41.76480188766095</v>
       </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J278" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -8809,6 +10481,12 @@
       <c r="H279" t="n">
         <v>-41.764544583491</v>
       </c>
+      <c r="I279" t="n">
+        <v>1</v>
+      </c>
+      <c r="J279" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -8839,6 +10517,12 @@
       <c r="H280" t="n">
         <v>-41.76475895513584</v>
       </c>
+      <c r="I280" t="n">
+        <v>1</v>
+      </c>
+      <c r="J280" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -8869,6 +10553,12 @@
       <c r="H281" t="n">
         <v>-41.76467390833221</v>
       </c>
+      <c r="I281" t="n">
+        <v>1</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -8899,6 +10589,12 @@
       <c r="H282" t="n">
         <v>-41.76462836628937</v>
       </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -8929,6 +10625,12 @@
       <c r="H283" t="n">
         <v>-41.7645866485649</v>
       </c>
+      <c r="I283" t="n">
+        <v>1</v>
+      </c>
+      <c r="J283" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -8959,6 +10661,12 @@
       <c r="H284" t="n">
         <v>-41.76454633827692</v>
       </c>
+      <c r="I284" t="n">
+        <v>1</v>
+      </c>
+      <c r="J284" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -8989,6 +10697,12 @@
       <c r="H285" t="n">
         <v>-41.76450501451325</v>
       </c>
+      <c r="I285" t="n">
+        <v>1</v>
+      </c>
+      <c r="J285" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -9019,6 +10733,12 @@
       <c r="H286" t="n">
         <v>-41.76445397752664</v>
       </c>
+      <c r="I286" t="n">
+        <v>1</v>
+      </c>
+      <c r="J286" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -9049,6 +10769,12 @@
       <c r="H287" t="n">
         <v>-41.76440371596745</v>
       </c>
+      <c r="I287" t="n">
+        <v>1</v>
+      </c>
+      <c r="J287" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -9079,6 +10805,12 @@
       <c r="H288" t="n">
         <v>-41.76519057472062</v>
       </c>
+      <c r="I288" t="n">
+        <v>1</v>
+      </c>
+      <c r="J288" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -9109,6 +10841,12 @@
       <c r="H289" t="n">
         <v>-41.76510100388926</v>
       </c>
+      <c r="I289" t="n">
+        <v>1</v>
+      </c>
+      <c r="J289" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -9139,6 +10877,12 @@
       <c r="H290" t="n">
         <v>-41.76450229400416</v>
       </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -9169,6 +10913,12 @@
       <c r="H291" t="n">
         <v>-41.76501189179763</v>
       </c>
+      <c r="I291" t="n">
+        <v>1</v>
+      </c>
+      <c r="J291" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -9199,6 +10949,12 @@
       <c r="H292" t="n">
         <v>-41.76496555956383</v>
       </c>
+      <c r="I292" t="n">
+        <v>1</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -9229,6 +10985,12 @@
       <c r="H293" t="n">
         <v>-41.76492292906154</v>
       </c>
+      <c r="I293" t="n">
+        <v>1</v>
+      </c>
+      <c r="J293" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -9259,6 +11021,12 @@
       <c r="H294" t="n">
         <v>-41.7648832505617</v>
       </c>
+      <c r="I294" t="n">
+        <v>1</v>
+      </c>
+      <c r="J294" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -9289,6 +11057,12 @@
       <c r="H295" t="n">
         <v>-41.76484171802161</v>
       </c>
+      <c r="I295" t="n">
+        <v>1</v>
+      </c>
+      <c r="J295" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -9319,6 +11093,12 @@
       <c r="H296" t="n">
         <v>-41.76480104482491</v>
       </c>
+      <c r="I296" t="n">
+        <v>1</v>
+      </c>
+      <c r="J296" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -9349,6 +11129,12 @@
       <c r="H297" t="n">
         <v>-41.76475595839881</v>
       </c>
+      <c r="I297" t="n">
+        <v>1</v>
+      </c>
+      <c r="J297" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -9379,6 +11165,12 @@
       <c r="H298" t="n">
         <v>-41.76471364385279</v>
       </c>
+      <c r="I298" t="n">
+        <v>1</v>
+      </c>
+      <c r="J298" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -9409,6 +11201,12 @@
       <c r="H299" t="n">
         <v>-41.7646718102508</v>
       </c>
+      <c r="I299" t="n">
+        <v>1</v>
+      </c>
+      <c r="J299" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -9439,6 +11237,12 @@
       <c r="H300" t="n">
         <v>-41.76463017787724</v>
       </c>
+      <c r="I300" t="n">
+        <v>1</v>
+      </c>
+      <c r="J300" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -9469,6 +11273,12 @@
       <c r="H301" t="n">
         <v>-41.76445365936538</v>
       </c>
+      <c r="I301" t="n">
+        <v>1</v>
+      </c>
+      <c r="J301" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -9499,6 +11309,12 @@
       <c r="H302" t="n">
         <v>-41.76459224363172</v>
       </c>
+      <c r="I302" t="n">
+        <v>1</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -9529,6 +11345,12 @@
       <c r="H303" t="n">
         <v>-41.76454470534429</v>
       </c>
+      <c r="I303" t="n">
+        <v>1</v>
+      </c>
+      <c r="J303" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -9559,6 +11381,12 @@
       <c r="H304" t="n">
         <v>-41.76450539218335</v>
       </c>
+      <c r="I304" t="n">
+        <v>1</v>
+      </c>
+      <c r="J304" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -9589,6 +11417,12 @@
       <c r="H305" t="n">
         <v>-41.76440282274278</v>
       </c>
+      <c r="I305" t="n">
+        <v>1</v>
+      </c>
+      <c r="J305" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -9619,6 +11453,12 @@
       <c r="H306" t="n">
         <v>-41.76519003385592</v>
       </c>
+      <c r="I306" t="n">
+        <v>1</v>
+      </c>
+      <c r="J306" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -9649,6 +11489,12 @@
       <c r="H307" t="n">
         <v>-41.76510057497257</v>
       </c>
+      <c r="I307" t="n">
+        <v>1</v>
+      </c>
+      <c r="J307" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -9679,6 +11525,12 @@
       <c r="H308" t="n">
         <v>-41.76492430473168</v>
       </c>
+      <c r="I308" t="n">
+        <v>1</v>
+      </c>
+      <c r="J308" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -9709,6 +11561,12 @@
       <c r="H309" t="n">
         <v>-41.76488299138592</v>
       </c>
+      <c r="I309" t="n">
+        <v>1</v>
+      </c>
+      <c r="J309" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -9739,6 +11597,12 @@
       <c r="H310" t="n">
         <v>-41.76483736285964</v>
       </c>
+      <c r="I310" t="n">
+        <v>1</v>
+      </c>
+      <c r="J310" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -9769,6 +11633,12 @@
       <c r="H311" t="n">
         <v>-41.76440267681914</v>
       </c>
+      <c r="I311" t="n">
+        <v>1</v>
+      </c>
+      <c r="J311" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -9799,6 +11669,12 @@
       <c r="H312" t="n">
         <v>-41.76492453785946</v>
       </c>
+      <c r="I312" t="n">
+        <v>1</v>
+      </c>
+      <c r="J312" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -9829,6 +11705,12 @@
       <c r="H313" t="n">
         <v>-41.76484314108604</v>
       </c>
+      <c r="I313" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -9859,6 +11741,12 @@
       <c r="H314" t="n">
         <v>-41.76480201587609</v>
       </c>
+      <c r="I314" t="n">
+        <v>1</v>
+      </c>
+      <c r="J314" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -9889,6 +11777,12 @@
       <c r="H315" t="n">
         <v>-41.76475748574099</v>
       </c>
+      <c r="I315" t="n">
+        <v>1</v>
+      </c>
+      <c r="J315" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -9919,6 +11813,12 @@
       <c r="H316" t="n">
         <v>-41.76467226650242</v>
       </c>
+      <c r="I316" t="n">
+        <v>1</v>
+      </c>
+      <c r="J316" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -9949,6 +11849,12 @@
       <c r="H317" t="n">
         <v>-41.76459054155523</v>
       </c>
+      <c r="I317" t="n">
+        <v>1</v>
+      </c>
+      <c r="J317" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -9979,6 +11885,12 @@
       <c r="H318" t="n">
         <v>-41.76454517537921</v>
       </c>
+      <c r="I318" t="n">
+        <v>1</v>
+      </c>
+      <c r="J318" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -10009,6 +11921,12 @@
       <c r="H319" t="n">
         <v>-41.76510512029514</v>
       </c>
+      <c r="I319" t="n">
+        <v>1</v>
+      </c>
+      <c r="J319" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -10039,6 +11957,12 @@
       <c r="H320" t="n">
         <v>-41.76501288350875</v>
       </c>
+      <c r="I320" t="n">
+        <v>1</v>
+      </c>
+      <c r="J320" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -10069,6 +11993,12 @@
       <c r="H321" t="n">
         <v>-41.76496611848023</v>
       </c>
+      <c r="I321" t="n">
+        <v>1</v>
+      </c>
+      <c r="J321" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -10099,6 +12029,12 @@
       <c r="H322" t="n">
         <v>-41.76492640507814</v>
       </c>
+      <c r="I322" t="n">
+        <v>1</v>
+      </c>
+      <c r="J322" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -10129,6 +12065,12 @@
       <c r="H323" t="n">
         <v>-41.76488446651202</v>
       </c>
+      <c r="I323" t="n">
+        <v>1</v>
+      </c>
+      <c r="J323" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -10159,6 +12101,12 @@
       <c r="H324" t="n">
         <v>-41.76450246277771</v>
       </c>
+      <c r="I324" t="n">
+        <v>1</v>
+      </c>
+      <c r="J324" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -10189,6 +12137,12 @@
       <c r="H325" t="n">
         <v>-41.76484489628807</v>
       </c>
+      <c r="I325" t="n">
+        <v>1</v>
+      </c>
+      <c r="J325" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -10219,6 +12173,12 @@
       <c r="H326" t="n">
         <v>-41.76480377114675</v>
       </c>
+      <c r="I326" t="n">
+        <v>1</v>
+      </c>
+      <c r="J326" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -10249,6 +12209,12 @@
       <c r="H327" t="n">
         <v>-41.76475924104598</v>
       </c>
+      <c r="I327" t="n">
+        <v>1</v>
+      </c>
+      <c r="J327" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -10279,6 +12245,12 @@
       <c r="H328" t="n">
         <v>-41.76467402180741</v>
       </c>
+      <c r="I328" t="n">
+        <v>1</v>
+      </c>
+      <c r="J328" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -10309,6 +12281,12 @@
       <c r="H329" t="n">
         <v>-41.76459229686022</v>
       </c>
+      <c r="I329" t="n">
+        <v>1</v>
+      </c>
+      <c r="J329" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -10339,6 +12317,12 @@
       <c r="H330" t="n">
         <v>-41.764504994855</v>
       </c>
+      <c r="I330" t="n">
+        <v>1</v>
+      </c>
+      <c r="J330" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -10369,6 +12353,12 @@
       <c r="H331" t="n">
         <v>-41.76454598949898</v>
       </c>
+      <c r="I331" t="n">
+        <v>1</v>
+      </c>
+      <c r="J331" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -10399,6 +12389,12 @@
       <c r="H332" t="n">
         <v>-41.76440393448399</v>
       </c>
+      <c r="I332" t="n">
+        <v>1</v>
+      </c>
+      <c r="J332" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -10429,6 +12425,12 @@
       <c r="H333" t="n">
         <v>-41.76519144552651</v>
       </c>
+      <c r="I333" t="n">
+        <v>1</v>
+      </c>
+      <c r="J333" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -10459,6 +12461,12 @@
       <c r="H334" t="n">
         <v>-41.76510136897292</v>
       </c>
+      <c r="I334" t="n">
+        <v>1</v>
+      </c>
+      <c r="J334" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -10489,6 +12497,12 @@
       <c r="H335" t="n">
         <v>-41.76501133428831</v>
       </c>
+      <c r="I335" t="n">
+        <v>1</v>
+      </c>
+      <c r="J335" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -10519,6 +12533,12 @@
       <c r="H336" t="n">
         <v>-41.76439978656484</v>
       </c>
+      <c r="I336" t="n">
+        <v>1</v>
+      </c>
+      <c r="J336" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -10549,6 +12569,12 @@
       <c r="H337" t="n">
         <v>-41.76547884386627</v>
       </c>
+      <c r="I337" t="n">
+        <v>1</v>
+      </c>
+      <c r="J337" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -10579,6 +12605,12 @@
       <c r="H338" t="n">
         <v>-41.7654111923317</v>
       </c>
+      <c r="I338" t="n">
+        <v>1</v>
+      </c>
+      <c r="J338" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -10609,6 +12641,12 @@
       <c r="H339" t="n">
         <v>-41.76534503620565</v>
       </c>
+      <c r="I339" t="n">
+        <v>1</v>
+      </c>
+      <c r="J339" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -10639,6 +12677,12 @@
       <c r="H340" t="n">
         <v>-41.76547829243137</v>
       </c>
+      <c r="I340" t="n">
+        <v>1</v>
+      </c>
+      <c r="J340" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -10669,6 +12713,12 @@
       <c r="H341" t="n">
         <v>-41.76541117146586</v>
       </c>
+      <c r="I341" t="n">
+        <v>1</v>
+      </c>
+      <c r="J341" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -10699,6 +12749,12 @@
       <c r="H342" t="n">
         <v>-41.76534435854612</v>
       </c>
+      <c r="I342" t="n">
+        <v>1</v>
+      </c>
+      <c r="J342" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -10729,6 +12785,12 @@
       <c r="H343" t="n">
         <v>-41.7654794192557</v>
       </c>
+      <c r="I343" t="n">
+        <v>1</v>
+      </c>
+      <c r="J343" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -10759,6 +12821,12 @@
       <c r="H344" t="n">
         <v>-41.76541096438606</v>
       </c>
+      <c r="I344" t="n">
+        <v>1</v>
+      </c>
+      <c r="J344" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -10789,6 +12857,12 @@
       <c r="H345" t="n">
         <v>-41.76534250958505</v>
       </c>
+      <c r="I345" t="n">
+        <v>1</v>
+      </c>
+      <c r="J345" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -10819,6 +12893,12 @@
       <c r="H346" t="n">
         <v>-41.76547840836037</v>
       </c>
+      <c r="I346" t="n">
+        <v>1</v>
+      </c>
+      <c r="J346" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -10849,6 +12929,12 @@
       <c r="H347" t="n">
         <v>-41.76540995349072</v>
       </c>
+      <c r="I347" t="n">
+        <v>1</v>
+      </c>
+      <c r="J347" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -10879,6 +12965,12 @@
       <c r="H348" t="n">
         <v>-41.76534149855244</v>
       </c>
+      <c r="I348" t="n">
+        <v>1</v>
+      </c>
+      <c r="J348" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -10909,6 +13001,12 @@
       <c r="H349" t="n">
         <v>-41.76548019472389</v>
       </c>
+      <c r="I349" t="n">
+        <v>1</v>
+      </c>
+      <c r="J349" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -10939,6 +13037,12 @@
       <c r="H350" t="n">
         <v>-41.76541207542373</v>
       </c>
+      <c r="I350" t="n">
+        <v>1</v>
+      </c>
+      <c r="J350" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -10969,6 +13073,12 @@
       <c r="H351" t="n">
         <v>-41.76534546587735</v>
       </c>
+      <c r="I351" t="n">
+        <v>1</v>
+      </c>
+      <c r="J351" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -10999,6 +13109,12 @@
       <c r="H352" t="n">
         <v>-41.76547882334361</v>
       </c>
+      <c r="I352" t="n">
+        <v>1</v>
+      </c>
+      <c r="J352" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -11029,6 +13145,12 @@
       <c r="H353" t="n">
         <v>-41.76541070418072</v>
       </c>
+      <c r="I353" t="n">
+        <v>1</v>
+      </c>
+      <c r="J353" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -11059,6 +13181,12 @@
       <c r="H354" t="n">
         <v>-41.76534409463434</v>
       </c>
+      <c r="I354" t="n">
+        <v>1</v>
+      </c>
+      <c r="J354" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -11089,6 +13217,12 @@
       <c r="H355" t="n">
         <v>-41.76547769789204</v>
       </c>
+      <c r="I355" t="n">
+        <v>1</v>
+      </c>
+      <c r="J355" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -11119,6 +13253,12 @@
       <c r="H356" t="n">
         <v>-41.76541004944617</v>
       </c>
+      <c r="I356" t="n">
+        <v>1</v>
+      </c>
+      <c r="J356" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -11149,6 +13289,12 @@
       <c r="H357" t="n">
         <v>-41.76534160617629</v>
       </c>
+      <c r="I357" t="n">
+        <v>1</v>
+      </c>
+      <c r="J357" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -11179,6 +13325,12 @@
       <c r="H358" t="n">
         <v>-41.76456116421989</v>
       </c>
+      <c r="I358" t="n">
+        <v>1</v>
+      </c>
+      <c r="J358" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -11209,6 +13361,12 @@
       <c r="H359" t="n">
         <v>-41.76547945474137</v>
       </c>
+      <c r="I359" t="n">
+        <v>1</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -11239,6 +13397,12 @@
       <c r="H360" t="n">
         <v>-41.76540943259959</v>
       </c>
+      <c r="I360" t="n">
+        <v>1</v>
+      </c>
+      <c r="J360" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -11269,6 +13433,12 @@
       <c r="H361" t="n">
         <v>-41.76534433555251</v>
       </c>
+      <c r="I361" t="n">
+        <v>1</v>
+      </c>
+      <c r="J361" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -11299,6 +13469,12 @@
       <c r="H362" t="n">
         <v>-41.76547892060317</v>
       </c>
+      <c r="I362" t="n">
+        <v>1</v>
+      </c>
+      <c r="J362" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -11329,6 +13505,12 @@
       <c r="H363" t="n">
         <v>-41.76540889818683</v>
       </c>
+      <c r="I363" t="n">
+        <v>1</v>
+      </c>
+      <c r="J363" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -11359,6 +13541,12 @@
       <c r="H364" t="n">
         <v>-41.76534380127703</v>
       </c>
+      <c r="I364" t="n">
+        <v>1</v>
+      </c>
+      <c r="J364" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -11389,6 +13577,12 @@
       <c r="H365" t="n">
         <v>-41.76520237401341</v>
       </c>
+      <c r="I365" t="n">
+        <v>1</v>
+      </c>
+      <c r="J365" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -11419,6 +13613,12 @@
       <c r="H366" t="n">
         <v>-41.76551080176282</v>
       </c>
+      <c r="I366" t="n">
+        <v>1</v>
+      </c>
+      <c r="J366" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -11449,6 +13649,12 @@
       <c r="H367" t="n">
         <v>-41.76541856435868</v>
       </c>
+      <c r="I367" t="n">
+        <v>1</v>
+      </c>
+      <c r="J367" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -11479,6 +13685,12 @@
       <c r="H368" t="n">
         <v>-41.76533024705675</v>
       </c>
+      <c r="I368" t="n">
+        <v>1</v>
+      </c>
+      <c r="J368" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -11509,6 +13721,12 @@
       <c r="H369" t="n">
         <v>-41.76523885471939</v>
       </c>
+      <c r="I369" t="n">
+        <v>1</v>
+      </c>
+      <c r="J369" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -11539,6 +13757,12 @@
       <c r="H370" t="n">
         <v>-41.76553821673912</v>
       </c>
+      <c r="I370" t="n">
+        <v>1</v>
+      </c>
+      <c r="J370" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -11569,6 +13793,12 @@
       <c r="H371" t="n">
         <v>-41.76547622314345</v>
       </c>
+      <c r="I371" t="n">
+        <v>1</v>
+      </c>
+      <c r="J371" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -11599,6 +13829,12 @@
       <c r="H372" t="n">
         <v>-41.76545052939355</v>
       </c>
+      <c r="I372" t="n">
+        <v>1</v>
+      </c>
+      <c r="J372" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -11629,6 +13865,12 @@
       <c r="H373" t="n">
         <v>-41.76536756733848</v>
       </c>
+      <c r="I373" t="n">
+        <v>1</v>
+      </c>
+      <c r="J373" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -11659,6 +13901,12 @@
       <c r="H374" t="n">
         <v>-41.76528339327975</v>
       </c>
+      <c r="I374" t="n">
+        <v>1</v>
+      </c>
+      <c r="J374" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -11689,6 +13937,12 @@
       <c r="H375" t="n">
         <v>-41.76519413708338</v>
       </c>
+      <c r="I375" t="n">
+        <v>1</v>
+      </c>
+      <c r="J375" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -11719,6 +13973,12 @@
       <c r="H376" t="n">
         <v>-41.76545039843291</v>
       </c>
+      <c r="I376" t="n">
+        <v>1</v>
+      </c>
+      <c r="J376" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -11749,6 +14009,12 @@
       <c r="H377" t="n">
         <v>-41.76536773124519</v>
       </c>
+      <c r="I377" t="n">
+        <v>1</v>
+      </c>
+      <c r="J377" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -11779,6 +14045,12 @@
       <c r="H378" t="n">
         <v>-41.76528326231912</v>
       </c>
+      <c r="I378" t="n">
+        <v>1</v>
+      </c>
+      <c r="J378" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -11809,6 +14081,12 @@
       <c r="H379" t="n">
         <v>-41.76519412301266</v>
       </c>
+      <c r="I379" t="n">
+        <v>1</v>
+      </c>
+      <c r="J379" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -11839,6 +14117,12 @@
       <c r="H380" t="n">
         <v>-41.76553963266523</v>
       </c>
+      <c r="I380" t="n">
+        <v>1</v>
+      </c>
+      <c r="J380" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -11869,6 +14153,12 @@
       <c r="H381" t="n">
         <v>-41.7654929277633</v>
       </c>
+      <c r="I381" t="n">
+        <v>1</v>
+      </c>
+      <c r="J381" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -11899,6 +14189,12 @@
       <c r="H382" t="n">
         <v>-41.76536733424501</v>
       </c>
+      <c r="I382" t="n">
+        <v>1</v>
+      </c>
+      <c r="J382" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -11929,6 +14225,12 @@
       <c r="H383" t="n">
         <v>-41.76545087951421</v>
       </c>
+      <c r="I383" t="n">
+        <v>1</v>
+      </c>
+      <c r="J383" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -11959,6 +14261,12 @@
       <c r="H384" t="n">
         <v>-41.76541107159807</v>
       </c>
+      <c r="I384" t="n">
+        <v>1</v>
+      </c>
+      <c r="J384" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -11989,6 +14297,12 @@
       <c r="H385" t="n">
         <v>-41.76536949722333</v>
       </c>
+      <c r="I385" t="n">
+        <v>1</v>
+      </c>
+      <c r="J385" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -12019,6 +14333,12 @@
       <c r="H386" t="n">
         <v>-41.76532901501091</v>
       </c>
+      <c r="I386" t="n">
+        <v>1</v>
+      </c>
+      <c r="J386" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -12049,6 +14369,12 @@
       <c r="H387" t="n">
         <v>-41.76528367709644</v>
       </c>
+      <c r="I387" t="n">
+        <v>1</v>
+      </c>
+      <c r="J387" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -12079,6 +14405,12 @@
       <c r="H388" t="n">
         <v>-41.76553741717911</v>
       </c>
+      <c r="I388" t="n">
+        <v>1</v>
+      </c>
+      <c r="J388" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -12109,6 +14441,12 @@
       <c r="H389" t="n">
         <v>-41.76545190743168</v>
       </c>
+      <c r="I389" t="n">
+        <v>1</v>
+      </c>
+      <c r="J389" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -12139,6 +14477,12 @@
       <c r="H390" t="n">
         <v>-41.7654105936741</v>
       </c>
+      <c r="I390" t="n">
+        <v>1</v>
+      </c>
+      <c r="J390" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -12169,6 +14513,12 @@
       <c r="H391" t="n">
         <v>-41.76536519659399</v>
       </c>
+      <c r="I391" t="n">
+        <v>1</v>
+      </c>
+      <c r="J391" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -12199,6 +14549,12 @@
       <c r="H392" t="n">
         <v>-41.76532772627036</v>
       </c>
+      <c r="I392" t="n">
+        <v>1</v>
+      </c>
+      <c r="J392" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -12229,6 +14585,12 @@
       <c r="H393" t="n">
         <v>-41.76526263670478</v>
       </c>
+      <c r="I393" t="n">
+        <v>1</v>
+      </c>
+      <c r="J393" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -12259,6 +14621,12 @@
       <c r="H394" t="n">
         <v>-41.76528505238907</v>
       </c>
+      <c r="I394" t="n">
+        <v>1</v>
+      </c>
+      <c r="J394" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -12289,6 +14657,12 @@
       <c r="H395" t="n">
         <v>-41.76547818734714</v>
       </c>
+      <c r="I395" t="n">
+        <v>1</v>
+      </c>
+      <c r="J395" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -12319,6 +14693,12 @@
       <c r="H396" t="n">
         <v>-41.76540918522949</v>
       </c>
+      <c r="I396" t="n">
+        <v>1</v>
+      </c>
+      <c r="J396" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -12349,6 +14729,12 @@
       <c r="H397" t="n">
         <v>-41.76534128467753</v>
       </c>
+      <c r="I397" t="n">
+        <v>1</v>
+      </c>
+      <c r="J397" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -12379,6 +14765,12 @@
       <c r="H398" t="n">
         <v>-41.76547807038857</v>
       </c>
+      <c r="I398" t="n">
+        <v>1</v>
+      </c>
+      <c r="J398" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -12409,6 +14801,12 @@
       <c r="H399" t="n">
         <v>-41.76540906840821</v>
       </c>
+      <c r="I399" t="n">
+        <v>1</v>
+      </c>
+      <c r="J399" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -12439,6 +14837,12 @@
       <c r="H400" t="n">
         <v>-41.76520218580897</v>
       </c>
+      <c r="I400" t="n">
+        <v>1</v>
+      </c>
+      <c r="J400" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -12469,6 +14873,12 @@
       <c r="H401" t="n">
         <v>-41.76500978160167</v>
       </c>
+      <c r="I401" t="n">
+        <v>1</v>
+      </c>
+      <c r="J401" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -12499,6 +14909,12 @@
       <c r="H402" t="n">
         <v>-41.76534116771897</v>
       </c>
+      <c r="I402" t="n">
+        <v>1</v>
+      </c>
+      <c r="J402" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -12529,6 +14945,12 @@
       <c r="H403" t="n">
         <v>-41.76547561707299</v>
       </c>
+      <c r="I403" t="n">
+        <v>1</v>
+      </c>
+      <c r="J403" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -12559,6 +14981,12 @@
       <c r="H404" t="n">
         <v>-41.7654077872178</v>
       </c>
+      <c r="I404" t="n">
+        <v>1</v>
+      </c>
+      <c r="J404" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -12589,6 +15017,12 @@
       <c r="H405" t="n">
         <v>-41.76530421897284</v>
       </c>
+      <c r="I405" t="n">
+        <v>1</v>
+      </c>
+      <c r="J405" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -12619,6 +15053,12 @@
       <c r="H406" t="n">
         <v>-41.76536884427335</v>
       </c>
+      <c r="I406" t="n">
+        <v>1</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -12649,6 +15089,12 @@
       <c r="H407" t="n">
         <v>-41.76528461928549</v>
       </c>
+      <c r="I407" t="n">
+        <v>1</v>
+      </c>
+      <c r="J407" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -12679,6 +15125,12 @@
       <c r="H408" t="n">
         <v>-41.76519573599748</v>
       </c>
+      <c r="I408" t="n">
+        <v>1</v>
+      </c>
+      <c r="J408" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -12709,6 +15161,12 @@
       <c r="H409" t="n">
         <v>-41.76553888732897</v>
       </c>
+      <c r="I409" t="n">
+        <v>1</v>
+      </c>
+      <c r="J409" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -12739,6 +15197,12 @@
       <c r="H410" t="n">
         <v>-41.76545169829276</v>
       </c>
+      <c r="I410" t="n">
+        <v>1</v>
+      </c>
+      <c r="J410" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -12769,6 +15233,12 @@
       <c r="H411" t="n">
         <v>-41.76537065397368</v>
       </c>
+      <c r="I411" t="n">
+        <v>1</v>
+      </c>
+      <c r="J411" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -12799,6 +15269,12 @@
       <c r="H412" t="n">
         <v>-41.76532934762896</v>
       </c>
+      <c r="I412" t="n">
+        <v>1</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -12829,6 +15305,12 @@
       <c r="H413" t="n">
         <v>-41.76528490392583</v>
       </c>
+      <c r="I413" t="n">
+        <v>1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -12859,6 +15341,12 @@
       <c r="H414" t="n">
         <v>-41.76469911293589</v>
       </c>
+      <c r="I414" t="n">
+        <v>1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -12889,6 +15377,12 @@
       <c r="H415" t="n">
         <v>-41.76463074250772</v>
       </c>
+      <c r="I415" t="n">
+        <v>1</v>
+      </c>
+      <c r="J415" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -12919,6 +15413,12 @@
       <c r="H416" t="n">
         <v>-41.76456300513319</v>
       </c>
+      <c r="I416" t="n">
+        <v>1</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -12949,6 +15449,12 @@
       <c r="H417" t="n">
         <v>-41.76494964619884</v>
       </c>
+      <c r="I417" t="n">
+        <v>1</v>
+      </c>
+      <c r="J417" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -12979,6 +15485,12 @@
       <c r="H418" t="n">
         <v>-41.76488145812374</v>
       </c>
+      <c r="I418" t="n">
+        <v>1</v>
+      </c>
+      <c r="J418" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -13009,6 +15521,12 @@
       <c r="H419" t="n">
         <v>-41.76481290537681</v>
       </c>
+      <c r="I419" t="n">
+        <v>1</v>
+      </c>
+      <c r="J419" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -13039,6 +15557,12 @@
       <c r="H420" t="n">
         <v>-41.76469804311513</v>
       </c>
+      <c r="I420" t="n">
+        <v>1</v>
+      </c>
+      <c r="J420" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -13069,6 +15593,12 @@
       <c r="H421" t="n">
         <v>-41.76462967268696</v>
       </c>
+      <c r="I421" t="n">
+        <v>1</v>
+      </c>
+      <c r="J421" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -13099,6 +15629,12 @@
       <c r="H422" t="n">
         <v>-41.76495071598527</v>
       </c>
+      <c r="I422" t="n">
+        <v>1</v>
+      </c>
+      <c r="J422" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -13129,6 +15665,12 @@
       <c r="H423" t="n">
         <v>-41.76488252797882</v>
       </c>
+      <c r="I423" t="n">
+        <v>1</v>
+      </c>
+      <c r="J423" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -13159,6 +15701,12 @@
       <c r="H424" t="n">
         <v>-41.76481397516325</v>
       </c>
+      <c r="I424" t="n">
+        <v>1</v>
+      </c>
+      <c r="J424" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -13189,6 +15737,12 @@
       <c r="H425" t="n">
         <v>-41.76456193529527</v>
       </c>
+      <c r="I425" t="n">
+        <v>1</v>
+      </c>
+      <c r="J425" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -13219,6 +15773,12 @@
       <c r="H426" t="n">
         <v>-41.76495116919968</v>
       </c>
+      <c r="I426" t="n">
+        <v>1</v>
+      </c>
+      <c r="J426" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -13249,6 +15809,12 @@
       <c r="H427" t="n">
         <v>-41.76488340647212</v>
       </c>
+      <c r="I427" t="n">
+        <v>1</v>
+      </c>
+      <c r="J427" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -13279,6 +15845,12 @@
       <c r="H428" t="n">
         <v>-41.76481655545849</v>
       </c>
+      <c r="I428" t="n">
+        <v>1</v>
+      </c>
+      <c r="J428" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -13309,6 +15881,12 @@
       <c r="H429" t="n">
         <v>-41.76469865457365</v>
       </c>
+      <c r="I429" t="n">
+        <v>1</v>
+      </c>
+      <c r="J429" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -13339,6 +15917,12 @@
       <c r="H430" t="n">
         <v>-41.7646300731705</v>
       </c>
+      <c r="I430" t="n">
+        <v>1</v>
+      </c>
+      <c r="J430" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -13369,6 +15953,12 @@
       <c r="H431" t="n">
         <v>-41.76456339096259</v>
       </c>
+      <c r="I431" t="n">
+        <v>1</v>
+      </c>
+      <c r="J431" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -13399,6 +15989,12 @@
       <c r="H432" t="n">
         <v>-41.76428721413244</v>
       </c>
+      <c r="I432" t="n">
+        <v>3</v>
+      </c>
+      <c r="J432" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -13429,6 +16025,12 @@
       <c r="H433" t="n">
         <v>-41.76547679709149</v>
       </c>
+      <c r="I433" t="n">
+        <v>1</v>
+      </c>
+      <c r="J433" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -13459,6 +16061,12 @@
       <c r="H434" t="n">
         <v>-41.76540897361961</v>
       </c>
+      <c r="I434" t="n">
+        <v>1</v>
+      </c>
+      <c r="J434" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -13489,6 +16097,12 @@
       <c r="H435" t="n">
         <v>-41.76456007699091</v>
       </c>
+      <c r="I435" t="n">
+        <v>1</v>
+      </c>
+      <c r="J435" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -13519,6 +16133,12 @@
       <c r="H436" t="n">
         <v>-41.76400982460369</v>
       </c>
+      <c r="I436" t="n">
+        <v>1</v>
+      </c>
+      <c r="J436" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -13549,6 +16169,12 @@
       <c r="H437" t="n">
         <v>-41.76414451405222</v>
       </c>
+      <c r="I437" t="n">
+        <v>1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -13579,6 +16205,12 @@
       <c r="H438" t="n">
         <v>-41.76407476934383</v>
       </c>
+      <c r="I438" t="n">
+        <v>1</v>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -13609,6 +16241,12 @@
       <c r="H439" t="n">
         <v>-41.76440297021078</v>
       </c>
+      <c r="I439" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -13639,6 +16277,12 @@
       <c r="H440" t="n">
         <v>-41.76458584744339</v>
       </c>
+      <c r="I440" t="n">
+        <v>1</v>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -13669,6 +16313,12 @@
       <c r="H441" t="n">
         <v>-41.76445305829688</v>
       </c>
+      <c r="I441" t="n">
+        <v>1</v>
+      </c>
+      <c r="J441" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -13699,6 +16349,12 @@
       <c r="H442" t="n">
         <v>-41.76440282910892</v>
       </c>
+      <c r="I442" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -13729,6 +16385,12 @@
       <c r="H443" t="n">
         <v>-41.76536639905701</v>
       </c>
+      <c r="I443" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -13759,6 +16421,12 @@
       <c r="H444" t="n">
         <v>-41.76500892050801</v>
       </c>
+      <c r="I444" t="n">
+        <v>1</v>
+      </c>
+      <c r="J444" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -13788,6 +16456,12 @@
       </c>
       <c r="H445" t="n">
         <v>-41.76488316768173</v>
+      </c>
+      <c r="I445" t="n">
+        <v>1</v>
+      </c>
+      <c r="J445" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
